--- a/research/traditional_assets/database/data/mexico/mexico_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_insurance_prop_cas.xlsx
@@ -588,82 +588,82 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.108</v>
+        <v>0.0667</v>
       </c>
       <c r="E2">
-        <v>0.253</v>
+        <v>0.166</v>
       </c>
       <c r="F2">
-        <v>-0.0664</v>
+        <v>0.0472</v>
       </c>
       <c r="G2">
-        <v>0.2601551060252725</v>
+        <v>0.1287441955401337</v>
       </c>
       <c r="H2">
-        <v>0.2601551060252725</v>
+        <v>0.1287441955401337</v>
       </c>
       <c r="I2">
-        <v>0.1519605184662942</v>
+        <v>0.0701638005817217</v>
       </c>
       <c r="J2">
-        <v>0.1161577400074393</v>
+        <v>0.06101200050584495</v>
       </c>
       <c r="K2">
-        <v>216.1</v>
+        <v>119.8</v>
       </c>
       <c r="L2">
-        <v>0.1171972449699007</v>
+        <v>0.06113180588865642</v>
       </c>
       <c r="M2">
-        <v>123.9</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="N2">
-        <v>0.06043312847527071</v>
+        <v>0.05554254945569473</v>
       </c>
       <c r="O2">
-        <v>0.5733456732993985</v>
+        <v>0.7921535893155259</v>
       </c>
       <c r="P2">
-        <v>79.59999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="Q2">
-        <v>0.03882548044093259</v>
+        <v>0.04471497132154981</v>
       </c>
       <c r="R2">
-        <v>0.3683479870430356</v>
+        <v>0.637729549248748</v>
       </c>
       <c r="S2">
-        <v>44.3</v>
+        <v>18.5</v>
       </c>
       <c r="T2">
-        <v>0.357546408393866</v>
+        <v>0.1949420442571127</v>
       </c>
       <c r="U2">
-        <v>108.6</v>
+        <v>116.8</v>
       </c>
       <c r="V2">
-        <v>0.05297044190810653</v>
+        <v>0.06836006086854735</v>
       </c>
       <c r="W2">
-        <v>0.2672520405639376</v>
+        <v>0.1255633581385599</v>
       </c>
       <c r="X2">
-        <v>0.06076470439450635</v>
+        <v>0.1025370374537216</v>
       </c>
       <c r="Y2">
-        <v>0.2064873361694313</v>
+        <v>0.0230263206848383</v>
       </c>
       <c r="Z2">
-        <v>2.503258213412979</v>
+        <v>2.317800118273211</v>
       </c>
       <c r="AA2">
-        <v>0.2907728167251118</v>
+        <v>0.1414136219885326</v>
       </c>
       <c r="AB2">
-        <v>0.06076470439450635</v>
+        <v>0.1025370374537216</v>
       </c>
       <c r="AC2">
-        <v>0.2300081123306055</v>
+        <v>0.03887658453481103</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -675,7 +675,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-108.6</v>
+        <v>-116.8</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -684,10 +684,10 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.05593325092707046</v>
+        <v>-0.07337605226787285</v>
       </c>
       <c r="AK2">
-        <v>-0.1283536225032502</v>
+        <v>-0.1430320842517757</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -699,7 +699,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-0.3574720210664911</v>
+        <v>-0.7053140096618358</v>
       </c>
     </row>
     <row r="3">
@@ -719,82 +719,82 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.108</v>
+        <v>0.0667</v>
       </c>
       <c r="E3">
-        <v>0.253</v>
+        <v>0.166</v>
       </c>
       <c r="F3">
-        <v>-0.0664</v>
+        <v>0.0472</v>
       </c>
       <c r="G3">
-        <v>0.2601551060252725</v>
+        <v>0.1287441955401337</v>
       </c>
       <c r="H3">
-        <v>0.2601551060252725</v>
+        <v>0.1287441955401337</v>
       </c>
       <c r="I3">
-        <v>0.1519605184662942</v>
+        <v>0.0701638005817217</v>
       </c>
       <c r="J3">
-        <v>0.1161577400074393</v>
+        <v>0.06101200050584495</v>
       </c>
       <c r="K3">
-        <v>216.1</v>
+        <v>119.8</v>
       </c>
       <c r="L3">
-        <v>0.1171972449699007</v>
+        <v>0.06113180588865642</v>
       </c>
       <c r="M3">
-        <v>123.9</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="N3">
-        <v>0.06043312847527071</v>
+        <v>0.05554254945569473</v>
       </c>
       <c r="O3">
-        <v>0.5733456732993985</v>
+        <v>0.7921535893155259</v>
       </c>
       <c r="P3">
-        <v>79.59999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="Q3">
-        <v>0.03882548044093259</v>
+        <v>0.04471497132154981</v>
       </c>
       <c r="R3">
-        <v>0.3683479870430356</v>
+        <v>0.637729549248748</v>
       </c>
       <c r="S3">
-        <v>44.3</v>
+        <v>18.5</v>
       </c>
       <c r="T3">
-        <v>0.357546408393866</v>
+        <v>0.1949420442571127</v>
       </c>
       <c r="U3">
-        <v>108.6</v>
+        <v>116.8</v>
       </c>
       <c r="V3">
-        <v>0.05297044190810653</v>
+        <v>0.06836006086854735</v>
       </c>
       <c r="W3">
-        <v>0.2672520405639376</v>
+        <v>0.1255633581385599</v>
       </c>
       <c r="X3">
-        <v>0.06076470439450635</v>
+        <v>0.1025370374537216</v>
       </c>
       <c r="Y3">
-        <v>0.2064873361694313</v>
+        <v>0.0230263206848383</v>
       </c>
       <c r="Z3">
-        <v>2.503258213412979</v>
+        <v>2.317800118273211</v>
       </c>
       <c r="AA3">
-        <v>0.2907728167251118</v>
+        <v>0.1414136219885326</v>
       </c>
       <c r="AB3">
-        <v>0.06076470439450635</v>
+        <v>0.1025370374537216</v>
       </c>
       <c r="AC3">
-        <v>0.2300081123306055</v>
+        <v>0.03887658453481103</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -806,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-108.6</v>
+        <v>-116.8</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -815,10 +815,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.05593325092707046</v>
+        <v>-0.07337605226787285</v>
       </c>
       <c r="AK3">
-        <v>-0.1283536225032502</v>
+        <v>-0.1430320842517757</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -830,7 +830,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.3574720210664911</v>
+        <v>-0.7053140096618358</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/mexico/mexico_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_insurance_prop_cas.xlsx
@@ -588,82 +588,82 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0667</v>
+        <v>0.0895</v>
       </c>
       <c r="E2">
-        <v>0.166</v>
+        <v>0.0462</v>
       </c>
       <c r="F2">
-        <v>0.0472</v>
+        <v>0.34</v>
       </c>
       <c r="G2">
-        <v>0.1287441955401337</v>
+        <v>0.05260756650522917</v>
       </c>
       <c r="H2">
-        <v>0.1287441955401337</v>
+        <v>0.05260756650522917</v>
       </c>
       <c r="I2">
-        <v>0.0701638005817217</v>
+        <v>0.08545658735172317</v>
       </c>
       <c r="J2">
-        <v>0.06101200050584495</v>
+        <v>0.06729795793540982</v>
       </c>
       <c r="K2">
-        <v>119.8</v>
+        <v>187.7</v>
       </c>
       <c r="L2">
-        <v>0.06113180588865642</v>
+        <v>0.06587351723169789</v>
       </c>
       <c r="M2">
-        <v>94.90000000000001</v>
+        <v>116.96</v>
       </c>
       <c r="N2">
-        <v>0.05554254945569473</v>
+        <v>0.02914890965732087</v>
       </c>
       <c r="O2">
-        <v>0.7921535893155259</v>
+        <v>0.6231220031965903</v>
       </c>
       <c r="P2">
-        <v>76.40000000000001</v>
+        <v>114</v>
       </c>
       <c r="Q2">
-        <v>0.04471497132154981</v>
+        <v>0.02841121495327103</v>
       </c>
       <c r="R2">
-        <v>0.637729549248748</v>
+        <v>0.607352157698455</v>
       </c>
       <c r="S2">
-        <v>18.5</v>
+        <v>2.959999999999994</v>
       </c>
       <c r="T2">
-        <v>0.1949420442571127</v>
+        <v>0.02530779753761965</v>
       </c>
       <c r="U2">
-        <v>116.8</v>
+        <v>205.6</v>
       </c>
       <c r="V2">
-        <v>0.06836006086854735</v>
+        <v>0.0512398753894081</v>
       </c>
       <c r="W2">
-        <v>0.1255633581385599</v>
+        <v>0.2013084513084513</v>
       </c>
       <c r="X2">
-        <v>0.1025370374537216</v>
+        <v>0.08756323367671123</v>
       </c>
       <c r="Y2">
-        <v>0.0230263206848383</v>
+        <v>0.1137452176317401</v>
       </c>
       <c r="Z2">
-        <v>2.317800118273211</v>
+        <v>3.493624325649828</v>
       </c>
       <c r="AA2">
-        <v>0.1414136219885326</v>
+        <v>0.2351137829097067</v>
       </c>
       <c r="AB2">
-        <v>0.1025370374537216</v>
+        <v>0.08756323367671123</v>
       </c>
       <c r="AC2">
-        <v>0.03887658453481103</v>
+        <v>0.1475505492329954</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -675,7 +675,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-116.8</v>
+        <v>-205.6</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -684,10 +684,10 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.07337605226787285</v>
+        <v>-0.05400719745724868</v>
       </c>
       <c r="AK2">
-        <v>-0.1430320842517757</v>
+        <v>-0.217290213485521</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -699,7 +699,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-0.7053140096618358</v>
+        <v>-0.7758490566037736</v>
       </c>
     </row>
     <row r="3">
@@ -719,82 +719,82 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0667</v>
+        <v>0.0895</v>
       </c>
       <c r="E3">
-        <v>0.166</v>
+        <v>0.0462</v>
       </c>
       <c r="F3">
-        <v>0.0472</v>
+        <v>0.34</v>
       </c>
       <c r="G3">
-        <v>0.1287441955401337</v>
+        <v>0.05260756650522917</v>
       </c>
       <c r="H3">
-        <v>0.1287441955401337</v>
+        <v>0.05260756650522917</v>
       </c>
       <c r="I3">
-        <v>0.0701638005817217</v>
+        <v>0.08545658735172317</v>
       </c>
       <c r="J3">
-        <v>0.06101200050584495</v>
+        <v>0.06729795793540982</v>
       </c>
       <c r="K3">
-        <v>119.8</v>
+        <v>187.7</v>
       </c>
       <c r="L3">
-        <v>0.06113180588865642</v>
+        <v>0.06587351723169789</v>
       </c>
       <c r="M3">
-        <v>94.90000000000001</v>
+        <v>116.96</v>
       </c>
       <c r="N3">
-        <v>0.05554254945569473</v>
+        <v>0.02914890965732087</v>
       </c>
       <c r="O3">
-        <v>0.7921535893155259</v>
+        <v>0.6231220031965903</v>
       </c>
       <c r="P3">
-        <v>76.40000000000001</v>
+        <v>114</v>
       </c>
       <c r="Q3">
-        <v>0.04471497132154981</v>
+        <v>0.02841121495327103</v>
       </c>
       <c r="R3">
-        <v>0.637729549248748</v>
+        <v>0.607352157698455</v>
       </c>
       <c r="S3">
-        <v>18.5</v>
+        <v>2.959999999999994</v>
       </c>
       <c r="T3">
-        <v>0.1949420442571127</v>
+        <v>0.02530779753761965</v>
       </c>
       <c r="U3">
-        <v>116.8</v>
+        <v>205.6</v>
       </c>
       <c r="V3">
-        <v>0.06836006086854735</v>
+        <v>0.0512398753894081</v>
       </c>
       <c r="W3">
-        <v>0.1255633581385599</v>
+        <v>0.2013084513084513</v>
       </c>
       <c r="X3">
-        <v>0.1025370374537216</v>
+        <v>0.08756323367671123</v>
       </c>
       <c r="Y3">
-        <v>0.0230263206848383</v>
+        <v>0.1137452176317401</v>
       </c>
       <c r="Z3">
-        <v>2.317800118273211</v>
+        <v>3.493624325649828</v>
       </c>
       <c r="AA3">
-        <v>0.1414136219885326</v>
+        <v>0.2351137829097067</v>
       </c>
       <c r="AB3">
-        <v>0.1025370374537216</v>
+        <v>0.08756323367671123</v>
       </c>
       <c r="AC3">
-        <v>0.03887658453481103</v>
+        <v>0.1475505492329954</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -806,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-116.8</v>
+        <v>-205.6</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -815,10 +815,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.07337605226787285</v>
+        <v>-0.05400719745724868</v>
       </c>
       <c r="AK3">
-        <v>-0.1430320842517757</v>
+        <v>-0.217290213485521</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -830,7 +830,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.7053140096618358</v>
+        <v>-0.7758490566037736</v>
       </c>
     </row>
   </sheetData>
